--- a/examples/v2_sample_new_format.xlsx
+++ b/examples/v2_sample_new_format.xlsx
@@ -449,12 +449,12 @@
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>每台上限</t>
+          <t>爆炸半徑 (1:x), EX: 2</t>
         </is>
       </c>
       <c r="E4" s="1" t="inlineStr">
         <is>
-          <t>共居</t>
+          <t>Tenant (自由=留空/指定群組/獨佔)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -608,12 +608,12 @@
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>每台上限</t>
+          <t>爆炸半徑 (1:x), EX: 2</t>
         </is>
       </c>
       <c r="E4" s="1" t="inlineStr">
         <is>
-          <t>共居</t>
+          <t>Tenant (自由=留空/指定群組/獨佔)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
